--- a/12629976.xlsx
+++ b/12629976.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/62266fe0ec916fa0/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="459" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9AFF298-7BC1-4BBD-9C4A-914BD6FEDC9C}"/>
+  <xr:revisionPtr revIDLastSave="460" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{272A6DEF-0CFF-4FBA-873A-1630A21398C4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -224,6 +224,30 @@
   </si>
   <si>
     <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>normal day</t>
+  </si>
+  <si>
+    <t>low energy</t>
+  </si>
+  <si>
+    <t>routine day</t>
+  </si>
+  <si>
+    <t>balanced day</t>
+  </si>
+  <si>
+    <t>good energy</t>
+  </si>
+  <si>
+    <t>good day</t>
+  </si>
+  <si>
+    <t>fine day</t>
+  </si>
+  <si>
+    <t>unexpected day</t>
   </si>
 </sst>
 </file>
@@ -1090,7 +1114,9 @@
       <c r="M7" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="N7" s="17"/>
+      <c r="N7" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="13">
@@ -1134,7 +1160,9 @@
       <c r="M8" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N8" s="17"/>
+      <c r="N8" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="13">
@@ -1178,7 +1206,9 @@
       <c r="M9" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="N9" s="17"/>
+      <c r="N9" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="13">
@@ -1222,7 +1252,9 @@
       <c r="M10" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N10" s="17"/>
+      <c r="N10" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="13">
@@ -1266,7 +1298,9 @@
       <c r="M11" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N11" s="17"/>
+      <c r="N11" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="13">
@@ -1310,7 +1344,9 @@
       <c r="M12" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N12" s="17"/>
+      <c r="N12" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="13">
@@ -1354,7 +1390,9 @@
       <c r="M13" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="N13" s="17"/>
+      <c r="N13" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="13">
@@ -1398,7 +1436,9 @@
       <c r="M14" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N14" s="17"/>
+      <c r="N14" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="13">
@@ -1442,7 +1482,9 @@
       <c r="M15" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N15" s="17"/>
+      <c r="N15" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="13">
@@ -1486,7 +1528,9 @@
       <c r="M16" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="N16" s="17"/>
+      <c r="N16" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="13">
@@ -1530,7 +1574,9 @@
       <c r="M17" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N17" s="17"/>
+      <c r="N17" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="13">
@@ -1574,7 +1620,9 @@
       <c r="M18" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="N18" s="17"/>
+      <c r="N18" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="13">
@@ -1618,7 +1666,9 @@
       <c r="M19" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N19" s="17"/>
+      <c r="N19" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="13">
@@ -1662,7 +1712,9 @@
       <c r="M20" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="N20" s="17"/>
+      <c r="N20" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="13">
@@ -1706,7 +1758,9 @@
       <c r="M21" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N21" s="17"/>
+      <c r="N21" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="13">
@@ -1750,7 +1804,9 @@
       <c r="M22" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="N22" s="17"/>
+      <c r="N22" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="13">
@@ -1794,7 +1850,9 @@
       <c r="M23" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N23" s="17"/>
+      <c r="N23" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="13">
@@ -1838,7 +1896,9 @@
       <c r="M24" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="N24" s="17"/>
+      <c r="N24" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="13">
@@ -1882,7 +1942,9 @@
       <c r="M25" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="N25" s="17"/>
+      <c r="N25" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="13">
@@ -1926,7 +1988,9 @@
       <c r="M26" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="N26" s="17"/>
+      <c r="N26" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="13">
@@ -1970,7 +2034,9 @@
       <c r="M27" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N27" s="17"/>
+      <c r="N27" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="13">
@@ -2014,7 +2080,9 @@
       <c r="M28" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N28" s="17"/>
+      <c r="N28" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="13">
@@ -2058,7 +2126,9 @@
       <c r="M29" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="N29" s="17"/>
+      <c r="N29" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="13">
@@ -2102,7 +2172,9 @@
       <c r="M30" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="N30" s="17"/>
+      <c r="N30" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="13">
@@ -2146,7 +2218,9 @@
       <c r="M31" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="N31" s="17"/>
+      <c r="N31" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="13"/>
